--- a/comps.xlsx
+++ b/comps.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/Nvme_1/ClaudeCode/earthUI/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7178E1E4-06CA-634F-9EF9-F7F177BC7396}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2036E85E-245D-A849-B44E-D94907E701C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="18700" yWindow="11080" windowWidth="26840" windowHeight="15680" xr2:uid="{22687250-4325-1E46-A626-79682C5983AB}"/>
+    <workbookView xWindow="61660" yWindow="12420" windowWidth="26840" windowHeight="15680" xr2:uid="{22687250-4325-1E46-A626-79682C5983AB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,29 +36,59 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="14">
   <si>
     <t>earthUI</t>
   </si>
   <si>
-    <t>glmnetUI</t>
-  </si>
-  <si>
-    <t>mgcvUI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  </t>
-  </si>
-  <si>
     <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>Method</t>
+  </si>
+  <si>
+    <t>Value Conc.</t>
+  </si>
+  <si>
+    <t>% Diff To earthUI</t>
+  </si>
+  <si>
+    <t>R2</t>
+  </si>
+  <si>
+    <t>CVR2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terms </t>
+  </si>
+  <si>
+    <t>Med Grs Adj</t>
+  </si>
+  <si>
+    <t>mgcvUI w/earth Import</t>
+  </si>
+  <si>
+    <t>glmnetUI w/earth Import</t>
+  </si>
+  <si>
+    <t>mcgvUI standalone</t>
+  </si>
+  <si>
+    <t>Low 6 GrsAdj</t>
+  </si>
+  <si>
+    <t>14-19%</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="0.000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="166" formatCode="0.0000"/>
+    <numFmt numFmtId="167" formatCode="0.0000%"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -116,15 +146,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -459,72 +494,147 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64740444-1A78-3F4F-BB52-913532884C85}">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="9.6640625" customWidth="1"/>
-    <col min="3" max="3" width="10.83203125" style="3"/>
+    <col min="1" max="1" width="21.83203125" customWidth="1"/>
+    <col min="2" max="2" width="10.83203125" customWidth="1"/>
+    <col min="3" max="3" width="14.1640625" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1">
+      <c r="B2" s="1">
         <v>3161998</v>
       </c>
-      <c r="C1" s="2"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
+      <c r="C2" s="6">
+        <v>0</v>
+      </c>
+      <c r="D2" s="3">
+        <v>0.88790000000000002</v>
+      </c>
+      <c r="E2" s="3">
+        <v>0.8579</v>
+      </c>
+      <c r="F2" s="1">
+        <v>36</v>
+      </c>
+      <c r="G2" s="4">
+        <v>0.94</v>
+      </c>
+      <c r="H2" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="1">
-        <v>3149134</v>
-      </c>
-      <c r="C2" s="2">
-        <f>B2/B1</f>
-        <v>0.99593168623130057</v>
-      </c>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1">
         <v>3168215</v>
       </c>
-      <c r="C3" s="2">
-        <f>B3/B1</f>
-        <v>1.0019661619014306</v>
-      </c>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
+      <c r="C3" s="6">
+        <f>B3/B2-1</f>
+        <v>1.9661619014306186E-3</v>
+      </c>
+      <c r="D3" s="3">
+        <v>0.88770000000000004</v>
+      </c>
+      <c r="E3" s="3">
+        <v>0.85089999999999999</v>
+      </c>
       <c r="F3" s="1"/>
+      <c r="G3" s="4">
+        <v>0.93</v>
+      </c>
+      <c r="H3" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B4" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" t="s">
-        <v>4</v>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="1">
+        <v>3174342</v>
+      </c>
+      <c r="C4" s="6">
+        <f>B4/B3-1</f>
+        <v>1.9338965316431089E-3</v>
+      </c>
+      <c r="D4" s="3">
+        <v>0.85940000000000005</v>
+      </c>
+      <c r="E4" s="3">
+        <v>0.8448</v>
+      </c>
+      <c r="F4" s="1">
+        <v>9</v>
+      </c>
+      <c r="G4" s="4">
+        <v>0.54</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B5">
-        <f>199/12</f>
-        <v>16.583333333333332</v>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="1">
+        <v>3135294</v>
+      </c>
+      <c r="C5" s="6">
+        <f>B5/B2-1</f>
+        <v>-8.4452931342777759E-3</v>
+      </c>
+      <c r="D5" s="3">
+        <v>0.85109999999999997</v>
+      </c>
+      <c r="E5" s="3">
+        <v>0.83320000000000005</v>
+      </c>
+      <c r="F5" s="1">
+        <v>6</v>
+      </c>
+      <c r="G5" s="4">
+        <v>0.47590000000000005</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B6" t="s">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1:B3">
-    <sortCondition ref="B1:B3"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G4">
+    <sortCondition ref="A2:A4"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
